--- a/app/data/raw/accesibilidad.xlsx
+++ b/app/data/raw/accesibilidad.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F908EE1D-93BF-42BD-9C3A-9923D0C9641C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -4470,5 +4470,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>